--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_75_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_75_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3978</v>
+        <v>7.8326</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8239</v>
+        <v>5.4268</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5738</v>
+        <v>2.4058</v>
       </c>
       <c r="G2" t="n">
         <v>3.5849</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1892</v>
+        <v>0.624</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6765</v>
+        <v>0.2794</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5127</v>
+        <v>0.3446</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.311</v>
+        <v>5.2861</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95</v>
+        <v>2.9251</v>
       </c>
       <c r="F3" t="n">
         <v>2.361</v>
@@ -688,10 +688,10 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5623</v>
+        <v>0.4127</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4402</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="U3" t="n">
         <v>-0.1221</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2432</v>
+        <v>3.7602</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7993</v>
+        <v>1.5515</v>
       </c>
       <c r="F4" t="n">
-        <v>2.444</v>
+        <v>2.2087</v>
       </c>
       <c r="G4" t="n">
         <v>1.5756</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>1.451</v>
+        <v>0.968</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9831</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4679</v>
+        <v>0.2326</v>
       </c>
       <c r="V4" t="n">
         <v>2.1444</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4021</v>
+        <v>0.9522</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9325</v>
+        <v>0.0203</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4696</v>
+        <v>0.9319</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7854</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4917</v>
+        <v>1.0418</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7695</v>
+        <v>0.8573</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7222</v>
+        <v>0.1845</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0813</v>
+        <v>0.3673</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4458</v>
+        <v>-0.3278</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5271</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0437</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5012</v>
+        <v>-0.2153</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V6" t="n">
         <v>0.3943</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5303</v>
+        <v>-0.4967</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0378</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4925</v>
+        <v>-0.4589</v>
       </c>
       <c r="G7" t="n">
         <v>-0.478</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0866</v>
+        <v>-1.046</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8858</v>
+        <v>-1.1385</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7993</v>
+        <v>0.0925</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7622</v>
+        <v>-0.5988</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.253</v>
+        <v>0.3783</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5091</v>
+        <v>-0.977</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6187</v>
+        <v>-0.4271</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2017</v>
+        <v>0.2857</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.8204</v>
+        <v>-0.7127</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1434</v>
+        <v>-0.1717</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4547</v>
+        <v>0.0926</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3113</v>
+        <v>-0.2643</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1937</v>
+        <v>0.2486</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0351</v>
+        <v>0.4483</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2289</v>
+        <v>-0.1997</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6599</v>
+        <v>-1.1634</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9267</v>
+        <v>-1.9291</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2668</v>
+        <v>0.7657</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4645</v>
+        <v>-1.7622</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7385</v>
+        <v>-0.253</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7261</v>
+        <v>-1.5091</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6855</v>
+        <v>-1.6187</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.2017</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0035</v>
+        <v>-1.8204</v>
       </c>
       <c r="M9" t="n">
-        <v>0.779</v>
+        <v>-0.1434</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0495</v>
+        <v>-0.4547</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7296</v>
+        <v>0.3113</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4476</v>
+        <v>0.1169</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0474</v>
+        <v>-0.0784</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4002</v>
+        <v>0.1953</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7886</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8187</v>
+        <v>-1.2142</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8776</v>
+        <v>-4.3802</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0589</v>
+        <v>3.166</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5988</v>
+        <v>1.4645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3783</v>
+        <v>0.7385</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.977</v>
+        <v>0.7261</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4271</v>
+        <v>0.6855</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2857</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>-0.0035</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1717</v>
+        <v>0.779</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0926</v>
+        <v>0.0495</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2643</v>
+        <v>0.7296</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5241</v>
+        <v>0.8933</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2908</v>
+        <v>0.5939</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2333</v>
+        <v>0.2994</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2532</v>
+        <v>-2.4208</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8167</v>
+        <v>-2.1523</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4365</v>
+        <v>-0.2685</v>
       </c>
       <c r="G11" t="n">
         <v>1.89</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0556</v>
+        <v>-0.2232</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.3064</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0848</v>
+        <v>0.0833</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3529</v>
+        <v>-3.5559</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6023</v>
+        <v>-3.0741</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7506</v>
+        <v>-0.4817</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5483</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2855</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6765</v>
+        <v>0.2047</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.391</v>
+        <v>-0.1221</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3302</v>
+        <v>-5.7776</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5622</v>
+        <v>-4.4129</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.768</v>
+        <v>-1.3647</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2982</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7099</v>
+        <v>-0.1573</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0351</v>
+        <v>0.1142</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6748</v>
+        <v>-0.2715</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4665</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.403600000000001</v>
+        <v>2.523800000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.649199999999999</v>
+        <v>-7.529</v>
       </c>
       <c r="F14" t="n">
         <v>10.0529</v>
@@ -1519,10 +1519,10 @@
         <v>-1.8238</v>
       </c>
       <c r="J14" t="n">
-        <v>7.058599999999999</v>
+        <v>7.058600000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>5.6883</v>
+        <v>5.688300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.3705</v>
@@ -1546,16 +1546,16 @@
         <v>18.5564</v>
       </c>
       <c r="S14" t="n">
-        <v>2.653299999999999</v>
+        <v>3.7734</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0075</v>
+        <v>3.1277</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6458</v>
+        <v>0.6458000000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2836000000000003</v>
+        <v>0.2836000000000012</v>
       </c>
       <c r="W14" t="n">
         <v>4.319900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1386</v>
+        <v>4.9769</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7446</v>
+        <v>1.919</v>
       </c>
       <c r="F15" t="n">
-        <v>3.394</v>
+        <v>3.0579</v>
       </c>
       <c r="G15" t="n">
         <v>0.3163</v>
@@ -1624,13 +1624,13 @@
         <v>3.4793</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2502</v>
+        <v>0.0885</v>
       </c>
       <c r="T15" t="n">
-        <v>0.716</v>
+        <v>-0.1096</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5342</v>
+        <v>0.1981</v>
       </c>
       <c r="V15" t="n">
         <v>1.3247</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5741</v>
+        <v>2.7586</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3038</v>
+        <v>2.1859</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2703</v>
+        <v>0.5728</v>
       </c>
       <c r="G16" t="n">
         <v>0.784</v>
@@ -1702,13 +1702,13 @@
         <v>3.2473</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2974</v>
+        <v>-0.1129</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0791</v>
+        <v>-0.0389</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3765</v>
+        <v>-0.074</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5922</v>
+        <v>2.3221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4345</v>
+        <v>0.9063</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1577</v>
+        <v>1.4158</v>
       </c>
       <c r="G17" t="n">
         <v>2.6126</v>
@@ -1780,13 +1780,13 @@
         <v>3.4793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0925</v>
+        <v>-0.3626</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5579</v>
+        <v>-0.0861</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5346</v>
+        <v>-0.2765</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. KONDIC</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2315</v>
+        <v>0.86</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8137</v>
+        <v>-0.1238</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0453</v>
+        <v>0.9838</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3917</v>
+        <v>0.5886</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2641</v>
+        <v>-1.1982</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6558</v>
+        <v>1.7869</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2271</v>
+        <v>1.6606</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8437</v>
+        <v>-0.6078</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0709</v>
+        <v>2.2685</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1646</v>
+        <v>-1.072</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5796</v>
+        <v>-0.5904</v>
       </c>
       <c r="O18" t="n">
-        <v>0.415</v>
+        <v>-0.4816</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>3.2473</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9129</v>
+        <v>-0.2801</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0351</v>
+        <v>-0.1608</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8777</v>
+        <v>-0.1193</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>K. KONDIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1301</v>
+        <v>0.4053</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5956</v>
+        <v>-0.9317</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7258</v>
+        <v>1.3369</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5886</v>
+        <v>-0.3917</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1982</v>
+        <v>0.2641</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7869</v>
+        <v>-0.6558</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6606</v>
+        <v>-0.2271</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6078</v>
+        <v>0.8437</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2685</v>
+        <v>-1.0709</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.072</v>
+        <v>-0.1646</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5904</v>
+        <v>-0.5796</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4816</v>
+        <v>0.415</v>
       </c>
       <c r="P19" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.6237</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2473</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.01</v>
+        <v>-0.7391</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.1531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3774</v>
+        <v>-0.586</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7252</v>
+        <v>-1.0448</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7917</v>
+        <v>-0.9096</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0665</v>
+        <v>-0.1352</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3638</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0149</v>
+        <v>-0.3047</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1845</v>
+        <v>-0.3025</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1994</v>
+        <v>-0.0022</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2829</v>
+        <v>-2.2265</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7468</v>
+        <v>-1.6904</v>
       </c>
       <c r="F22" t="n">
         <v>-0.5361</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5727</v>
+        <v>0.6291</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5727</v>
+        <v>0.6291</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1382</v>
+        <v>-3.4248</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3088</v>
+        <v>-3.719</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1705</v>
+        <v>0.2942</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1851</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5046</v>
+        <v>-0.7912</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4591</v>
+        <v>-0.3354</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7561</v>
+        <v>-5.0763</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.279299999999999</v>
+        <v>-7.6896</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5232</v>
+        <v>2.6133</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6029</v>
@@ -2326,13 +2326,13 @@
         <v>3.4793</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6739000000000001</v>
+        <v>0.0059</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5579</v>
+        <v>0.0318</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.116</v>
+        <v>-0.0259</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.403899999999999</v>
+        <v>-0.6174999999999997</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.053</v>
+        <v>-10.0529</v>
       </c>
       <c r="F25" t="n">
-        <v>8.6492</v>
+        <v>9.435400000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9461</v>
@@ -2377,16 +2377,16 @@
         <v>1.824</v>
       </c>
       <c r="J25" t="n">
-        <v>5.112500000000001</v>
+        <v>5.112499999999999</v>
       </c>
       <c r="K25" t="n">
         <v>1.918100000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.194399999999999</v>
+        <v>3.1944</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.0586</v>
+        <v>-7.058600000000001</v>
       </c>
       <c r="N25" t="n">
         <v>-5.6883</v>
@@ -2404,16 +2404,16 @@
         <v>22.0355</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6535</v>
+        <v>-1.8671</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6457000000000003</v>
+        <v>-0.6458999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0077</v>
+        <v>-1.2212</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2836000000000003</v>
+        <v>-0.2836000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>4.0363</v>
